--- a/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5310422602089269</v>
+        <v>0.5841813135985199</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7962421395353991</v>
+        <v>0.7160826260891231</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5310422602089269</v>
+        <v>0.5841813135985199</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7962421395353991</v>
+        <v>0.7160826260891231</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4843898385565053</v>
+        <v>0.3912529550827423</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7884511735304583</v>
+        <v>0.5931337590851656</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9938271604938271</v>
+        <v>0.9985096104430055</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9968181246857717</v>
+        <v>0.9986930091185411</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.6714285714285714</v>
       </c>
     </row>
   </sheetData>
